--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-28T01:08:35.257Z</t>
+    <t>2026-10-28T01:17:13.250Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
